--- a/supplementary_tables/working/cluster_pathway_summary.xlsx
+++ b/supplementary_tables/working/cluster_pathway_summary.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t xml:space="preserve">Cluster</t>
   </si>
@@ -337,6 +337,30 @@
 Hallmark: Allograft Rejection
 KEGG: Amoebiasis
 Hallmark: Tnfa Signaling via Nfkb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Th1/Th2 Effector Hyper-Activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Dysregulated Repair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Effector Cytokine &amp; Chemokine Activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Exhaustion &amp; Chronic Inflammation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Neuroinflammation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Niche Homeostasis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Neuro-Recovery Failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Interferons &amp; Cytotoxicity</t>
   </si>
 </sst>
 </file>
@@ -804,7 +828,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="B3" t="n">
         <v>12</v>
@@ -860,7 +884,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="B7" t="n">
         <v>13</v>
@@ -899,7 +923,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -913,7 +937,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B3" t="n">
         <v>41</v>
@@ -941,7 +965,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="B5" t="n">
         <v>9</v>
@@ -955,7 +979,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="B6" t="n">
         <v>30</v>
@@ -969,7 +993,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="B7" t="n">
         <v>19</v>
@@ -1036,7 +1060,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B4" t="n">
         <v>21</v>
